--- a/tables/abbreviations.xlsx
+++ b/tables/abbreviations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20369"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andy\OneDrive - University College London\SCUA\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\choic\CASA\london-cooling-access-equity-thesis\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FABBC144-B1AF-4C66-8BAE-906D6C490CE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEBF4C4-278C-435B-88E9-02238E73EFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7485" xr2:uid="{2919A5B8-BF7C-4943-B2AE-9E8EB0A96388}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{2919A5B8-BF7C-4943-B2AE-9E8EB0A96388}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Term</t>
   </si>
@@ -33,22 +33,148 @@
     <t>Abbreviation</t>
   </si>
   <si>
-    <t>DEM</t>
-  </si>
-  <si>
-    <t>DSM</t>
-  </si>
-  <si>
-    <t>DTM</t>
-  </si>
-  <si>
-    <t>Digital Elevation Model</t>
-  </si>
-  <si>
-    <t>Digital Surface Model</t>
-  </si>
-  <si>
-    <t>Digital Terrain Model</t>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>Akaike Information Criterion</t>
+  </si>
+  <si>
+    <t>BHM</t>
+  </si>
+  <si>
+    <t>Bayesian Hierarchical Models</t>
+  </si>
+  <si>
+    <t>BiLISA</t>
+  </si>
+  <si>
+    <t>Bivariate Local Indicators of Spatial Association</t>
+  </si>
+  <si>
+    <t>BYM2</t>
+  </si>
+  <si>
+    <t>Besag-York-Mollié</t>
+  </si>
+  <si>
+    <t>CPO</t>
+  </si>
+  <si>
+    <t>Conditional Predictive Ordinate</t>
+  </si>
+  <si>
+    <t>DIC</t>
+  </si>
+  <si>
+    <t>Deviance Information Criterion</t>
+  </si>
+  <si>
+    <t>Environmental justice</t>
+  </si>
+  <si>
+    <t>EJ</t>
+  </si>
+  <si>
+    <t>Generalised Linear Models</t>
+  </si>
+  <si>
+    <t>GLM</t>
+  </si>
+  <si>
+    <t>GTFS</t>
+  </si>
+  <si>
+    <t>INLA</t>
+  </si>
+  <si>
+    <t>L-H</t>
+  </si>
+  <si>
+    <t>LST</t>
+  </si>
+  <si>
+    <t>MLIK</t>
+  </si>
+  <si>
+    <t>OLS</t>
+  </si>
+  <si>
+    <t>PCG</t>
+  </si>
+  <si>
+    <t>PCI</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>SUHII</t>
+  </si>
+  <si>
+    <t>UGS</t>
+  </si>
+  <si>
+    <t>UHI</t>
+  </si>
+  <si>
+    <t>VIF</t>
+  </si>
+  <si>
+    <t>WAIC</t>
+  </si>
+  <si>
+    <t>General Transit Feed Specification</t>
+  </si>
+  <si>
+    <t>Integrated nested Laplace approximations</t>
+  </si>
+  <si>
+    <t>Low-High</t>
+  </si>
+  <si>
+    <t>Land Surface Temperature</t>
+  </si>
+  <si>
+    <t>Marginal likelihood</t>
+  </si>
+  <si>
+    <t>Ordinary Least Squares</t>
+  </si>
+  <si>
+    <t>Park cooling gradient</t>
+  </si>
+  <si>
+    <t>Park cooling intensity</t>
+  </si>
+  <si>
+    <t>Probability Integral Transform</t>
+  </si>
+  <si>
+    <t>Public transit</t>
+  </si>
+  <si>
+    <t>Remote sensing</t>
+  </si>
+  <si>
+    <t>Surface urban heat island intensity</t>
+  </si>
+  <si>
+    <t>Urban green space</t>
+  </si>
+  <si>
+    <t>Urban heat island</t>
+  </si>
+  <si>
+    <t>Variance Inflation Factors</t>
+  </si>
+  <si>
+    <t>Widely Applicable Information Criterion</t>
   </si>
 </sst>
 </file>
@@ -104,9 +230,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -144,7 +270,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -250,7 +376,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -392,7 +518,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -400,14 +526,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0918B5B-C1DF-4991-A3CC-9E87313077B4}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,28 +541,196 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
